--- a/data/kilder/anmeldte-forbrydelser-straf11.xlsx
+++ b/data/kilder/anmeldte-forbrydelser-straf11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <x:si>
     <x:t>Anmeldte forbrydelser efter overtrædelsens art, område og tid</x:t>
   </x:si>
@@ -355,16 +355,20 @@
     <x:t>Uoplyst kommune</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Antal anmeldelser for Love vedr. dyr, jagt mv. er for lavt i 2023. Der mangler ca. 1.700 anmeldelser.    
-  Straffelovens bestemmelser vedr. seksualforbrydelser gennemgik væsentlige ændringer med virkning fra 1. juli 2013. Ændringerne betød bl.a., at der nu er flere kategorier af seksualforbrydelser end tidligere, der henføres under bestemmelserne om voldtægt (§216). Se mere herom i statistikdokumentationen, i afsnittet Sammenlignelighed: http://www.dst.dk/statistikdokumentation/c1ac7749-1e15-4d3a-8ed0-fb2d26a9fe93 </x:t>
+    <x:t>Straffelov i alt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antal anmeldelser for Love vedr. dyr, jagt mv. er for lavt i 2023. Der mangler ca. 1.700 anmeldelser.    
+  Straffelovens bestemmelser vedr. seksualforbrydelser gennemgik væsentlige ændringer med virkning fra 1. juli 2013. Ændringerne betød bl.a., at der nu er flere kategorier af seksualforbrydelser end tidligere, der henføres under bestemmelserne om voldtægt (§216). Se mere herom i statistikdokumentationen, i afsnittet Sammenlignelighed: http://www.dst.dk/statistikdokumentation/c1ac7749-1e15-4d3a-8ed0-fb2d26a9fe93</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
+    <x:numFmt numFmtId="165" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -426,48 +430,45 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+  <x:cellStyleXfs count="5">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -478,7 +479,7 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -761,17 +762,17 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F111"/>
+  <x:dimension ref="A1:F217"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="40.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.270625" style="0" customWidth="1"/>
-    <x:col min="3" max="6" width="9.130625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.830625" style="0" customWidth="1"/>
+    <x:col min="3" max="6" width="8.300625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6">
@@ -2603,9 +2604,1814 @@
         <x:v>10075</x:v>
       </x:c>
     </x:row>
+    <x:row r="110" spans="1:6">
+      <x:c r="A110" s="3" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B110" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C110" s="4" t="n">
+        <x:v>75797</x:v>
+      </x:c>
+      <x:c r="D110" s="4" t="n">
+        <x:v>75288</x:v>
+      </x:c>
+      <x:c r="E110" s="4" t="n">
+        <x:v>77113</x:v>
+      </x:c>
+      <x:c r="F110" s="4" t="n">
+        <x:v>77641</x:v>
+      </x:c>
+    </x:row>
     <x:row r="111" spans="1:6">
-      <x:c r="A111" s="5" t="s">
+      <x:c r="B111" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C111" s="4" t="n">
+        <x:v>31375</x:v>
+      </x:c>
+      <x:c r="D111" s="4" t="n">
+        <x:v>30744</x:v>
+      </x:c>
+      <x:c r="E111" s="4" t="n">
+        <x:v>30371</x:v>
+      </x:c>
+      <x:c r="F111" s="4" t="n">
+        <x:v>30564</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:6">
+      <x:c r="B112" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C112" s="4" t="n">
+        <x:v>16072</x:v>
+      </x:c>
+      <x:c r="D112" s="4" t="n">
+        <x:v>15383</x:v>
+      </x:c>
+      <x:c r="E112" s="4" t="n">
+        <x:v>15323</x:v>
+      </x:c>
+      <x:c r="F112" s="4" t="n">
+        <x:v>14713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:6">
+      <x:c r="B113" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C113" s="4" t="n">
+        <x:v>1758</x:v>
+      </x:c>
+      <x:c r="D113" s="4" t="n">
+        <x:v>1849</x:v>
+      </x:c>
+      <x:c r="E113" s="4" t="n">
+        <x:v>1549</x:v>
+      </x:c>
+      <x:c r="F113" s="4" t="n">
+        <x:v>1574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:6">
+      <x:c r="B114" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C114" s="4" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D114" s="4" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E114" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F114" s="4" t="n">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:6">
+      <x:c r="B115" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C115" s="4" t="n">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c r="D115" s="4" t="n">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="E115" s="4" t="n">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="F115" s="4" t="n">
+        <x:v>841</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:6">
+      <x:c r="B116" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C116" s="4" t="n">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="D116" s="4" t="n">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="E116" s="4" t="n">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="F116" s="4" t="n">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:6">
+      <x:c r="B117" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C117" s="4" t="n">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="D117" s="4" t="n">
+        <x:v>786</x:v>
+      </x:c>
+      <x:c r="E117" s="4" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F117" s="4" t="n">
+        <x:v>685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:6">
+      <x:c r="B118" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C118" s="4" t="n">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="D118" s="4" t="n">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="E118" s="4" t="n">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="F118" s="4" t="n">
+        <x:v>459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:6">
+      <x:c r="B119" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C119" s="4" t="n">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="D119" s="4" t="n">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="E119" s="4" t="n">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="F119" s="4" t="n">
+        <x:v>1093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:6">
+      <x:c r="B120" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C120" s="4" t="n">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="D120" s="4" t="n">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="E120" s="4" t="n">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="F120" s="4" t="n">
+        <x:v>854</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:6">
+      <x:c r="B121" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C121" s="4" t="n">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D121" s="4" t="n">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="E121" s="4" t="n">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="F121" s="4" t="n">
+        <x:v>486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:6">
+      <x:c r="B122" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C122" s="4" t="n">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D122" s="4" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="E122" s="4" t="n">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="F122" s="4" t="n">
+        <x:v>410</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:6">
+      <x:c r="B123" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C123" s="4" t="n">
+        <x:v>741</x:v>
+      </x:c>
+      <x:c r="D123" s="4" t="n">
+        <x:v>739</x:v>
+      </x:c>
+      <x:c r="E123" s="4" t="n">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="F123" s="4" t="n">
+        <x:v>767</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:6">
+      <x:c r="B124" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C124" s="4" t="n">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="D124" s="4" t="n">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E124" s="4" t="n">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="F124" s="4" t="n">
+        <x:v>673</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:6">
+      <x:c r="B125" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C125" s="4" t="n">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="D125" s="4" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="E125" s="4" t="n">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="F125" s="4" t="n">
+        <x:v>383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:6">
+      <x:c r="B126" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C126" s="4" t="n">
+        <x:v>759</x:v>
+      </x:c>
+      <x:c r="D126" s="4" t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="E126" s="4" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="F126" s="4" t="n">
+        <x:v>786</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:6">
+      <x:c r="B127" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C127" s="4" t="n">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="D127" s="4" t="n">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="E127" s="4" t="n">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="F127" s="4" t="n">
+        <x:v>675</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:6">
+      <x:c r="B128" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C128" s="4" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D128" s="4" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="E128" s="4" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F128" s="4" t="n">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:6">
+      <x:c r="B129" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C129" s="4" t="n">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D129" s="4" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E129" s="4" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F129" s="4" t="n">
+        <x:v>282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:6">
+      <x:c r="B130" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C130" s="4" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="D130" s="4" t="n">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="E130" s="4" t="n">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="F130" s="4" t="n">
+        <x:v>364</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:6">
+      <x:c r="B131" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C131" s="4" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="D131" s="4" t="n">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="E131" s="4" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F131" s="4" t="n">
+        <x:v>425</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:6">
+      <x:c r="B132" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C132" s="4" t="n">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="D132" s="4" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="E132" s="4" t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="F132" s="4" t="n">
+        <x:v>469</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:6">
+      <x:c r="B133" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C133" s="4" t="n">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D133" s="4" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E133" s="4" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="F133" s="4" t="n">
+        <x:v>464</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:6">
+      <x:c r="B134" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C134" s="4" t="n">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="D134" s="4" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="E134" s="4" t="n">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="F134" s="4" t="n">
+        <x:v>388</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:6">
+      <x:c r="B135" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C135" s="4" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D135" s="4" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="E135" s="4" t="n">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="F135" s="4" t="n">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:6">
+      <x:c r="B136" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C136" s="4" t="n">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="D136" s="4" t="n">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="E136" s="4" t="n">
+        <x:v>833</x:v>
+      </x:c>
+      <x:c r="F136" s="4" t="n">
+        <x:v>933</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:6">
+      <x:c r="B137" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C137" s="4" t="n">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="D137" s="4" t="n">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="E137" s="4" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="F137" s="4" t="n">
+        <x:v>783</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:6">
+      <x:c r="B138" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C138" s="4" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D138" s="4" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="E138" s="4" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F138" s="4" t="n">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:6">
+      <x:c r="B139" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C139" s="4" t="n">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="D139" s="4" t="n">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="E139" s="4" t="n">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="F139" s="4" t="n">
+        <x:v>593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:6">
+      <x:c r="B140" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C140" s="4" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D140" s="4" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E140" s="4" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F140" s="4" t="n">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:6">
+      <x:c r="B141" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C141" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D141" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E141" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F141" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:6">
+      <x:c r="B142" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C142" s="4" t="n">
+        <x:v>8205</x:v>
+      </x:c>
+      <x:c r="D142" s="4" t="n">
+        <x:v>8150</x:v>
+      </x:c>
+      <x:c r="E142" s="4" t="n">
+        <x:v>9197</x:v>
+      </x:c>
+      <x:c r="F142" s="4" t="n">
+        <x:v>8533</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:6">
+      <x:c r="B143" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C143" s="4" t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="D143" s="4" t="n">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="E143" s="4" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="F143" s="4" t="n">
+        <x:v>574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:6">
+      <x:c r="B144" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C144" s="4" t="n">
+        <x:v>749</x:v>
+      </x:c>
+      <x:c r="D144" s="4" t="n">
+        <x:v>734</x:v>
+      </x:c>
+      <x:c r="E144" s="4" t="n">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="F144" s="4" t="n">
+        <x:v>678</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:6">
+      <x:c r="B145" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C145" s="4" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D145" s="4" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="E145" s="4" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F145" s="4" t="n">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:6">
+      <x:c r="B146" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C146" s="4" t="n">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c r="D146" s="4" t="n">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="E146" s="4" t="n">
+        <x:v>1636</x:v>
+      </x:c>
+      <x:c r="F146" s="4" t="n">
+        <x:v>881</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:6">
+      <x:c r="B147" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C147" s="4" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D147" s="4" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="E147" s="4" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F147" s="4" t="n">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:6">
+      <x:c r="B148" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C148" s="4" t="n">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="D148" s="4" t="n">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="E148" s="4" t="n">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="F148" s="4" t="n">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:6">
+      <x:c r="B149" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C149" s="4" t="n">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="D149" s="4" t="n">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="E149" s="4" t="n">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="F149" s="4" t="n">
+        <x:v>550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:6">
+      <x:c r="B150" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C150" s="4" t="n">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="D150" s="4" t="n">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="E150" s="4" t="n">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="F150" s="4" t="n">
+        <x:v>671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:6">
+      <x:c r="B151" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C151" s="4" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="D151" s="4" t="n">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="E151" s="4" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="F151" s="4" t="n">
+        <x:v>438</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:6">
+      <x:c r="B152" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C152" s="4" t="n">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="D152" s="4" t="n">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="E152" s="4" t="n">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="F152" s="4" t="n">
+        <x:v>478</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:6">
+      <x:c r="B153" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C153" s="4" t="n">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="D153" s="4" t="n">
+        <x:v>798</x:v>
+      </x:c>
+      <x:c r="E153" s="4" t="n">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="F153" s="4" t="n">
+        <x:v>942</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:6">
+      <x:c r="B154" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C154" s="4" t="n">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="D154" s="4" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="E154" s="4" t="n">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="F154" s="4" t="n">
+        <x:v>322</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:6">
+      <x:c r="B155" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C155" s="4" t="n">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="D155" s="4" t="n">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E155" s="4" t="n">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="F155" s="4" t="n">
+        <x:v>331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:6">
+      <x:c r="B156" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C156" s="4" t="n">
+        <x:v>921</x:v>
+      </x:c>
+      <x:c r="D156" s="4" t="n">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="E156" s="4" t="n">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="F156" s="4" t="n">
+        <x:v>1121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:6">
+      <x:c r="B157" s="3" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C157" s="4" t="n">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D157" s="4" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="E157" s="4" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F157" s="4" t="n">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:6">
+      <x:c r="B158" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C158" s="4" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D158" s="4" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="E158" s="4" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F158" s="4" t="n">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:6">
+      <x:c r="B159" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C159" s="4" t="n">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="D159" s="4" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="E159" s="4" t="n">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="F159" s="4" t="n">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:6">
+      <x:c r="B160" s="3" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C160" s="4" t="n">
+        <x:v>11929</x:v>
+      </x:c>
+      <x:c r="D160" s="4" t="n">
+        <x:v>12324</x:v>
+      </x:c>
+      <x:c r="E160" s="4" t="n">
+        <x:v>12210</x:v>
+      </x:c>
+      <x:c r="F160" s="4" t="n">
+        <x:v>13204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:6">
+      <x:c r="B161" s="3" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C161" s="4" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D161" s="4" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="E161" s="4" t="n">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F161" s="4" t="n">
+        <x:v>372</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:6">
+      <x:c r="B162" s="3" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C162" s="4" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="D162" s="4" t="n">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="E162" s="4" t="n">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="F162" s="4" t="n">
+        <x:v>437</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:6">
+      <x:c r="B163" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C163" s="4" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D163" s="4" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="E163" s="4" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F163" s="4" t="n">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:6">
+      <x:c r="B164" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C164" s="4" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D164" s="4" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E164" s="4" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F164" s="4" t="n">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:6">
+      <x:c r="B165" s="3" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C165" s="4" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="D165" s="4" t="n">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="E165" s="4" t="n">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="F165" s="4" t="n">
+        <x:v>415</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:6">
+      <x:c r="B166" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C166" s="4" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D166" s="4" t="n">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="E166" s="4" t="n">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F166" s="4" t="n">
+        <x:v>414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:6">
+      <x:c r="B167" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C167" s="4" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D167" s="4" t="n">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="E167" s="4" t="n">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="F167" s="4" t="n">
+        <x:v>359</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:6">
+      <x:c r="B168" s="3" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C168" s="4" t="n">
+        <x:v>2439</x:v>
+      </x:c>
+      <x:c r="D168" s="4" t="n">
+        <x:v>2986</x:v>
+      </x:c>
+      <x:c r="E168" s="4" t="n">
+        <x:v>2970</x:v>
+      </x:c>
+      <x:c r="F168" s="4" t="n">
+        <x:v>3608</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:6">
+      <x:c r="B169" s="3" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C169" s="4" t="n">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="D169" s="4" t="n">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="E169" s="4" t="n">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="F169" s="4" t="n">
+        <x:v>501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:6">
+      <x:c r="B170" s="3" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C170" s="4" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D170" s="4" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E170" s="4" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F170" s="4" t="n">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:6">
+      <x:c r="B171" s="3" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C171" s="4" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D171" s="4" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="E171" s="4" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F171" s="4" t="n">
+        <x:v>275</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:6">
+      <x:c r="B172" s="3" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C172" s="4" t="n">
+        <x:v>1419</x:v>
+      </x:c>
+      <x:c r="D172" s="4" t="n">
+        <x:v>1179</x:v>
+      </x:c>
+      <x:c r="E172" s="4" t="n">
+        <x:v>1287</x:v>
+      </x:c>
+      <x:c r="F172" s="4" t="n">
+        <x:v>1174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:6">
+      <x:c r="B173" s="3" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C173" s="4" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D173" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E173" s="4" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F173" s="4" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:6">
+      <x:c r="B174" s="3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C174" s="4" t="n">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="D174" s="4" t="n">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="E174" s="4" t="n">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="F174" s="4" t="n">
+        <x:v>707</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:6">
+      <x:c r="B175" s="3" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C175" s="4" t="n">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="D175" s="4" t="n">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="E175" s="4" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="F175" s="4" t="n">
+        <x:v>483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:6">
+      <x:c r="B176" s="3" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C176" s="4" t="n">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="D176" s="4" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="E176" s="4" t="n">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="F176" s="4" t="n">
+        <x:v>894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:6">
+      <x:c r="B177" s="3" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C177" s="4" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="D177" s="4" t="n">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="E177" s="4" t="n">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="F177" s="4" t="n">
+        <x:v>539</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:6">
+      <x:c r="B178" s="3" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C178" s="4" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="D178" s="4" t="n">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="E178" s="4" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="F178" s="4" t="n">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:6">
+      <x:c r="B179" s="3" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C179" s="4" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="D179" s="4" t="n">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="E179" s="4" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="F179" s="4" t="n">
+        <x:v>342</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:6">
+      <x:c r="B180" s="3" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C180" s="4" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="D180" s="4" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="E180" s="4" t="n">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F180" s="4" t="n">
+        <x:v>288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:6">
+      <x:c r="B181" s="3" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C181" s="4" t="n">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="D181" s="4" t="n">
+        <x:v>1222</x:v>
+      </x:c>
+      <x:c r="E181" s="4" t="n">
+        <x:v>1205</x:v>
+      </x:c>
+      <x:c r="F181" s="4" t="n">
+        <x:v>1294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:6">
+      <x:c r="B182" s="3" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C182" s="4" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="D182" s="4" t="n">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="E182" s="4" t="n">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="F182" s="4" t="n">
+        <x:v>462</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:6">
+      <x:c r="B183" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C183" s="4" t="n">
+        <x:v>12898</x:v>
+      </x:c>
+      <x:c r="D183" s="4" t="n">
+        <x:v>13103</x:v>
+      </x:c>
+      <x:c r="E183" s="4" t="n">
+        <x:v>14290</x:v>
+      </x:c>
+      <x:c r="F183" s="4" t="n">
+        <x:v>12927</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:6">
+      <x:c r="B184" s="3" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C184" s="4" t="n">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D184" s="4" t="n">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="E184" s="4" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F184" s="4" t="n">
+        <x:v>258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:6">
+      <x:c r="B185" s="3" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C185" s="4" t="n">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="D185" s="4" t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="E185" s="4" t="n">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="F185" s="4" t="n">
+        <x:v>324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:6">
+      <x:c r="B186" s="3" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C186" s="4" t="n">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c r="D186" s="4" t="n">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="E186" s="4" t="n">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="F186" s="4" t="n">
+        <x:v>855</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:6">
+      <x:c r="B187" s="3" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C187" s="4" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="D187" s="4" t="n">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="E187" s="4" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="F187" s="4" t="n">
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:6">
+      <x:c r="B188" s="3" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C188" s="4" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D188" s="4" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E188" s="4" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F188" s="4" t="n">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:6">
+      <x:c r="B189" s="3" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C189" s="4" t="n">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="D189" s="4" t="n">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="E189" s="4" t="n">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="F189" s="4" t="n">
+        <x:v>892</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:6">
+      <x:c r="B190" s="3" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C190" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D190" s="4" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E190" s="4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F190" s="4" t="n">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:6">
+      <x:c r="B191" s="3" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C191" s="4" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D191" s="4" t="n">
+        <x:v>801</x:v>
+      </x:c>
+      <x:c r="E191" s="4" t="n">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="F191" s="4" t="n">
+        <x:v>764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:6">
+      <x:c r="B192" s="3" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C192" s="4" t="n">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="D192" s="4" t="n">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="E192" s="4" t="n">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="F192" s="4" t="n">
+        <x:v>399</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:6">
+      <x:c r="B193" s="3" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C193" s="4" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D193" s="4" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="E193" s="4" t="n">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="F193" s="4" t="n">
+        <x:v>356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:6">
+      <x:c r="B194" s="3" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C194" s="4" t="n">
+        <x:v>5284</x:v>
+      </x:c>
+      <x:c r="D194" s="4" t="n">
+        <x:v>5475</x:v>
+      </x:c>
+      <x:c r="E194" s="4" t="n">
+        <x:v>5937</x:v>
+      </x:c>
+      <x:c r="F194" s="4" t="n">
+        <x:v>5010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:6">
+      <x:c r="B195" s="3" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C195" s="4" t="n">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="D195" s="4" t="n">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="E195" s="4" t="n">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="F195" s="4" t="n">
+        <x:v>899</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:6">
+      <x:c r="B196" s="3" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C196" s="4" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="D196" s="4" t="n">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="E196" s="4" t="n">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="F196" s="4" t="n">
+        <x:v>555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:6">
+      <x:c r="B197" s="3" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C197" s="4" t="n">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="D197" s="4" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="E197" s="4" t="n">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="F197" s="4" t="n">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:6">
+      <x:c r="B198" s="3" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C198" s="4" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D198" s="4" t="n">
         <x:v>113</x:v>
+      </x:c>
+      <x:c r="E198" s="4" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F198" s="4" t="n">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:6">
+      <x:c r="B199" s="3" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C199" s="4" t="n">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="D199" s="4" t="n">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="E199" s="4" t="n">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="F199" s="4" t="n">
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:6">
+      <x:c r="B200" s="3" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C200" s="4" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="D200" s="4" t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="E200" s="4" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F200" s="4" t="n">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:6">
+      <x:c r="B201" s="3" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C201" s="4" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D201" s="4" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E201" s="4" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F201" s="4" t="n">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:6">
+      <x:c r="B202" s="3" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C202" s="4" t="n">
+        <x:v>795</x:v>
+      </x:c>
+      <x:c r="D202" s="4" t="n">
+        <x:v>760</x:v>
+      </x:c>
+      <x:c r="E202" s="4" t="n">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="F202" s="4" t="n">
+        <x:v>836</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:6">
+      <x:c r="B203" s="3" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C203" s="4" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="D203" s="4" t="n">
+        <x:v>4719</x:v>
+      </x:c>
+      <x:c r="E203" s="4" t="n">
+        <x:v>4999</x:v>
+      </x:c>
+      <x:c r="F203" s="4" t="n">
+        <x:v>4445</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:6">
+      <x:c r="B204" s="3" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C204" s="4" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D204" s="4" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="E204" s="4" t="n">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F204" s="4" t="n">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:6">
+      <x:c r="B205" s="3" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C205" s="4" t="n">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="D205" s="4" t="n">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="E205" s="4" t="n">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="F205" s="4" t="n">
+        <x:v>438</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:6">
+      <x:c r="B206" s="3" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C206" s="4" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="D206" s="4" t="n">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="E206" s="4" t="n">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="F206" s="4" t="n">
+        <x:v>437</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:6">
+      <x:c r="B207" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C207" s="4" t="n">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D207" s="4" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="E207" s="4" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F207" s="4" t="n">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:6">
+      <x:c r="B208" s="3" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C208" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D208" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E208" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F208" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:6">
+      <x:c r="B209" s="3" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C209" s="4" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D209" s="4" t="n">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="E209" s="4" t="n">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="F209" s="4" t="n">
+        <x:v>347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:6">
+      <x:c r="B210" s="3" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C210" s="4" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D210" s="4" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E210" s="4" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F210" s="4" t="n">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:6">
+      <x:c r="B211" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C211" s="4" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D211" s="4" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E211" s="4" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F211" s="4" t="n">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:6">
+      <x:c r="B212" s="3" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C212" s="4" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D212" s="4" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="E212" s="4" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F212" s="4" t="n">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:6">
+      <x:c r="B213" s="3" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C213" s="4" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="D213" s="4" t="n">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="E213" s="4" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F213" s="4" t="n">
+        <x:v>267</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:6">
+      <x:c r="B214" s="3" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C214" s="4" t="n">
+        <x:v>2096</x:v>
+      </x:c>
+      <x:c r="D214" s="4" t="n">
+        <x:v>2273</x:v>
+      </x:c>
+      <x:c r="E214" s="4" t="n">
+        <x:v>2265</x:v>
+      </x:c>
+      <x:c r="F214" s="4" t="n">
+        <x:v>2073</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:6">
+      <x:c r="B215" s="3" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C215" s="4" t="n">
+        <x:v>6860</x:v>
+      </x:c>
+      <x:c r="D215" s="4" t="n">
+        <x:v>6248</x:v>
+      </x:c>
+      <x:c r="E215" s="4" t="n">
+        <x:v>6046</x:v>
+      </x:c>
+      <x:c r="F215" s="4" t="n">
+        <x:v>7968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:6">
+      <x:c r="A217" s="5" t="s">
+        <x:v>114</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
